--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test5/PRODUCTS.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test5/PRODUCTS.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Table" r:id="rId3" sheetId="1"/>
     <sheet name="Column" r:id="rId4" sheetId="2"/>
     <sheet name="Query" r:id="rId5" sheetId="3"/>
+    <sheet name="File" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
@@ -83,17 +84,72 @@
     </comment>
     <comment ref="C1" authorId="0">
       <text>
-        <t>offset for SELECT SQL.</t>
+        <t>This is an MVEL expression that creates a map that maps columns in the data source to columns in the table.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
-        <t>limit for SELECT SQL.</t>
+        <t>offset for SELECT SQL.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
+        <t>limit for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
         <t>NEXT_VALUE OR RANDOM</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <t>Specify the weighting for random data selection using the MVEL formula. By default, the weight for each row is 1.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <t>If the name given here is set to the group name of the column sheet, the results of the SELECT SQL will be used.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>This is an MVEL expression that reads data sources such as files and returns an iterable of Map objects.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <t>This is an MVEL expression that creates a map that maps columns in the data source to columns in the table.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <t>offset for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <t>limit for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <t>NEXT_VALUE OR RANDOM</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <t>Specify the weighting for random data selection using the MVEL formula. By default, the weight for each row is 1.</t>
       </text>
     </comment>
   </commentList>
@@ -101,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>Table Name</t>
   </si>
@@ -228,6 +284,9 @@
     <t>Select SQL</t>
   </si>
   <si>
+    <t>Column Mapping Expression</t>
+  </si>
+  <si>
     <t>Offset</t>
   </si>
   <si>
@@ -235,6 +294,9 @@
   </si>
   <si>
     <t>Selection Strategy</t>
+  </si>
+  <si>
+    <t>Selection Strategy weight expression</t>
   </si>
   <si>
     <t>Group1</t>
@@ -251,19 +313,182 @@
   <si>
     <t>NEXT_VALUE</t>
   </si>
+  <si>
+    <t>DataSource Expression</t>
+  </si>
+  <si>
+    <t>FileGroup1</t>
+  </si>
+  <si>
+    <t>[
+	["a":"1", "b":2]
+	,["a":"3", "b":4]
+]</t>
+  </si>
+  <si>
+    <t>[
+"col_a":a
+,"col_b":b
+,"col_c":"cccc"
+]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="489">
+  <fonts count="525">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -2276,7 +2501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="left" vertical="center"/>
@@ -2995,11 +3220,11 @@
     <xf numFmtId="0" fontId="478" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="480" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="482" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="480" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="484" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="center" wrapText="true"/>
@@ -3008,6 +3233,60 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="488" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -3023,6 +3302,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
@@ -3406,14 +3689,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.4921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="19.6171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="5.85546875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.73828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.85546875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="30.3671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3432,23 +3717,96 @@
       <c r="E1" s="239" t="s">
         <v>36</v>
       </c>
+      <c r="F1" s="240" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="241" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2" ht="105.0" customHeight="true">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="242" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="243" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="244"/>
+      <c r="D2" s="245" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="246" t="n">
+        <v>2.147483647E9</v>
+      </c>
+      <c r="F2" s="247" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="248"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="15.4921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.2265625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.73828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.85546875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="30.3671875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="249" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="250" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="251" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="252" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="253" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="254" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="241" t="s">
+      <c r="G1" s="255" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="242" t="n">
+    </row>
+    <row r="2" ht="75.0" customHeight="true">
+      <c r="A2" s="256" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="257" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="258" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="259" t="n">
         <v>0.0</v>
       </c>
-      <c r="D2" s="243" t="n">
+      <c r="E2" s="260" t="n">
         <v>2.147483647E9</v>
       </c>
-      <c r="E2" s="244" t="s">
-        <v>39</v>
-      </c>
+      <c r="F2" s="261" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="262"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
